--- a/calculations/System_Calculations.xlsx
+++ b/calculations/System_Calculations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bobbystyles/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9763568C-A485-C540-9D07-10C419F9EE2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C206C0D9-2430-D54A-95F3-5DE1A1DA2EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1820" yWindow="980" windowWidth="19720" windowHeight="13780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1820" yWindow="980" windowWidth="26420" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Component_Specs" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="65">
   <si>
     <t>Rail</t>
   </si>
@@ -61,12 +61,6 @@
     <t>Wheel Motor 4</t>
   </si>
   <si>
-    <t>Wheel Motor 5</t>
-  </si>
-  <si>
-    <t>Wheel Motor 6</t>
-  </si>
-  <si>
     <t>Arm Motor 1</t>
   </si>
   <si>
@@ -76,15 +70,6 @@
     <t>Arm Motor 3</t>
   </si>
   <si>
-    <t>Arm Motor 4</t>
-  </si>
-  <si>
-    <t>Arm Motor 5</t>
-  </si>
-  <si>
-    <t>Arm Motor 6</t>
-  </si>
-  <si>
     <t>Jetson</t>
   </si>
   <si>
@@ -245,6 +230,9 @@
   </si>
   <si>
     <t>Total Ah For Phase</t>
+  </si>
+  <si>
+    <t>Extra Value</t>
   </si>
 </sst>
 </file>
@@ -720,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -740,22 +728,22 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
       </c>
       <c r="H1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -766,10 +754,10 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -786,7 +774,7 @@
         <v>720</v>
       </c>
       <c r="K2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -797,32 +785,32 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F27" si="0">A3*E3</f>
+        <f t="shared" ref="F3:F23" si="0">A3*E3</f>
         <v>72</v>
       </c>
       <c r="G3">
         <v>30</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H27" si="1">A3*G3</f>
+        <f t="shared" ref="H3:H23" si="1">A3*G3</f>
         <v>720</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="L3" s="1">
-        <f>SUMIF($D$2:$D$27,"Rover",$E$2:$E$27)
-+ SUMIF($D$2:$D$27,"Arm",$E$2:$E$27)</f>
-        <v>143</v>
+        <f>SUMIF($D$2:$D$23,"Rover",$E$2:$E$23)
++ SUMIF($D$2:$D$23,"Arm",$E$2:$E$23)</f>
+        <v>39.299999999999997</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -833,10 +821,10 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -853,12 +841,12 @@
         <v>720</v>
       </c>
       <c r="K4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L4" s="1">
-        <f>SUMIF($D$2:$D$27,"Rover",$F$2:$F$27)
-+ SUMIF($D$2:$D$27,"Arm",$F$2:$F$27)</f>
-        <v>3382.3</v>
+        <f>SUMIF($D$2:$D$23,"Rover",$F$2:$F$23)
++ SUMIF($D$2:$D$23,"Arm",$F$2:$F$23)</f>
+        <v>893.5</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -869,10 +857,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -897,27 +885,24 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>199.20000000000002</v>
       </c>
       <c r="G6">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H6">
         <f t="shared" si="1"/>
-        <v>720</v>
-      </c>
-      <c r="K6" t="s">
-        <v>30</v>
+        <v>840</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -928,32 +913,27 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>6.7</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>160.80000000000001</v>
       </c>
       <c r="G7">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H7">
         <f t="shared" si="1"/>
-        <v>720</v>
+        <v>840</v>
       </c>
       <c r="K7" t="s">
-        <v>33</v>
-      </c>
-      <c r="L7" s="1">
-        <f>SUMIF($D$2:$D$27,"Rover",$E$2:$E$27)
-+ SUMIF($D$2:$D$27,"LD",$E$2:$E$27)</f>
-        <v>58.6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -964,17 +944,17 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>6.5</v>
       </c>
       <c r="F8">
         <f t="shared" si="0"/>
-        <v>480</v>
+        <v>156</v>
       </c>
       <c r="G8">
         <v>35</v>
@@ -984,12 +964,12 @@
         <v>840</v>
       </c>
       <c r="K8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="L8" s="1">
-        <f>SUMIF($D$2:$D$27,"Rover",$F$2:$F$27)
-+ SUMIF($D$2:$D$27,"LD",$F$2:$F$27)</f>
-        <v>1282.3999999999999</v>
+        <f>SUMIF($D$2:$D$23,"Rover",$E$2:$E$23)
++ SUMIF($D$2:$D$23,"LD",$E$2:$E$23)</f>
+        <v>52.6</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -997,20 +977,20 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>0.8</v>
       </c>
       <c r="F9">
         <f t="shared" si="0"/>
-        <v>480</v>
+        <v>19.200000000000003</v>
       </c>
       <c r="G9">
         <v>35</v>
@@ -1019,33 +999,41 @@
         <f t="shared" si="1"/>
         <v>840</v>
       </c>
+      <c r="K9" t="s">
+        <v>29</v>
+      </c>
+      <c r="L9" s="1">
+        <f>SUMIF($D$2:$D$23,"Rover",$F$2:$F$23)
++ SUMIF($D$2:$D$23,"LD",$F$2:$F$23)</f>
+        <v>1138.3999999999999</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E10">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F10">
         <f t="shared" si="0"/>
-        <v>480</v>
+        <v>384</v>
       </c>
       <c r="G10">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H10">
         <f t="shared" si="1"/>
-        <v>840</v>
+        <v>720</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -1053,27 +1041,27 @@
         <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F11">
         <f t="shared" si="0"/>
-        <v>480</v>
+        <v>192</v>
       </c>
       <c r="G11">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="H11">
         <f t="shared" si="1"/>
-        <v>840</v>
+        <v>384</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
@@ -1081,27 +1069,27 @@
         <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F12">
         <f t="shared" si="0"/>
-        <v>480</v>
+        <v>192</v>
       </c>
       <c r="G12">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="H12">
         <f t="shared" si="1"/>
-        <v>840</v>
+        <v>384</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
@@ -1112,192 +1100,192 @@
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F13">
         <f t="shared" si="0"/>
-        <v>480</v>
+        <v>24</v>
       </c>
       <c r="G13">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="H13">
         <f t="shared" si="1"/>
-        <v>840</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E14">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F14">
         <f t="shared" si="0"/>
-        <v>384</v>
+        <v>38</v>
       </c>
       <c r="G14">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="H14">
         <f t="shared" si="1"/>
-        <v>720</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E15">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F15">
         <f t="shared" si="0"/>
-        <v>192</v>
+        <v>5</v>
       </c>
       <c r="G15">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H15">
         <f t="shared" si="1"/>
-        <v>384</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>24</v>
+        <v>3.3</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E16">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="F16">
         <f t="shared" si="0"/>
-        <v>192</v>
+        <v>1.65</v>
       </c>
       <c r="G16">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H16">
         <f t="shared" si="1"/>
-        <v>384</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>24</v>
+        <v>3.3</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F17">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>1.65</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17">
         <f t="shared" si="1"/>
-        <v>48</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>19</v>
+        <v>3.3</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="F18">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>1.65</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18">
         <f t="shared" si="1"/>
-        <v>57</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F19">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>1.65</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H19">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -1305,13 +1293,13 @@
         <v>3.3</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E20">
         <v>0.5</v>
@@ -1333,13 +1321,13 @@
         <v>3.3</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E21">
         <v>0.5</v>
@@ -1361,13 +1349,13 @@
         <v>3.3</v>
       </c>
       <c r="B22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" t="s">
         <v>20</v>
-      </c>
-      <c r="C22" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22" t="s">
-        <v>25</v>
       </c>
       <c r="E22">
         <v>0.5</v>
@@ -1386,140 +1374,28 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" t="s">
         <v>20</v>
       </c>
-      <c r="C23" t="s">
-        <v>57</v>
-      </c>
-      <c r="D23" t="s">
-        <v>25</v>
-      </c>
       <c r="E23">
-        <v>0.5</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F23">
         <f t="shared" si="0"/>
-        <v>1.65</v>
+        <v>3.8500000000000005</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23">
-        <f t="shared" si="1"/>
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>3.3</v>
-      </c>
-      <c r="B24" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" t="s">
-        <v>57</v>
-      </c>
-      <c r="D24" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24">
-        <v>0.5</v>
-      </c>
-      <c r="F24">
-        <f t="shared" si="0"/>
-        <v>1.65</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24">
-        <f t="shared" si="1"/>
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>3.3</v>
-      </c>
-      <c r="B25" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25">
-        <v>0.5</v>
-      </c>
-      <c r="F25">
-        <f t="shared" si="0"/>
-        <v>1.65</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-      <c r="H25">
-        <f t="shared" si="1"/>
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>3.3</v>
-      </c>
-      <c r="B26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" t="s">
-        <v>25</v>
-      </c>
-      <c r="E26">
-        <v>0.5</v>
-      </c>
-      <c r="F26">
-        <f t="shared" si="0"/>
-        <v>1.65</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-      <c r="H26">
-        <f t="shared" si="1"/>
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>3.5</v>
-      </c>
-      <c r="B27" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" t="s">
-        <v>57</v>
-      </c>
-      <c r="D27" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F27">
-        <f t="shared" si="0"/>
-        <v>3.8500000000000005</v>
-      </c>
-      <c r="G27">
-        <v>2</v>
-      </c>
-      <c r="H27">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
@@ -1541,23 +1417,23 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="27" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B3">
         <v>5</v>
@@ -1565,7 +1441,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>10</v>
@@ -1573,7 +1449,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -1581,7 +1457,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -1589,15 +1465,15 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="27" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B9">
         <v>10</v>
@@ -1605,7 +1481,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>10</v>
@@ -1613,7 +1489,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -1621,7 +1497,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B12">
         <v>10</v>
@@ -1629,7 +1505,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B13">
         <v>10</v>
@@ -1637,7 +1513,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B14">
         <v>10</v>
@@ -1645,15 +1521,15 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="27" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B17">
         <v>5</v>
@@ -1661,7 +1537,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B18">
         <v>25</v>
@@ -1669,15 +1545,15 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="27" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B21">
         <v>30</v>
@@ -1707,13 +1583,13 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B1" s="4" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
       <c r="E1" s="8"/>
       <c r="F1" s="4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
@@ -1721,57 +1597,57 @@
       <c r="J1" s="7"/>
       <c r="K1" s="8"/>
       <c r="L1" s="4" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="M1" s="8"/>
       <c r="N1" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B2" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="I2" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="J2" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E2" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="6" t="s">
+      <c r="K2" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="H2" s="16" t="s">
+      <c r="L2" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="I2" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="J2" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="M2" s="17" t="s">
-        <v>53</v>
-      </c>
       <c r="N2" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B3" s="9">
         <v>1</v>
@@ -1815,7 +1691,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B4" s="9">
         <v>0</v>
@@ -1859,7 +1735,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B5" s="9">
         <v>0</v>
@@ -1903,7 +1779,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B6" s="9">
         <v>0</v>
@@ -1947,7 +1823,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B7" s="9">
         <v>1</v>
@@ -2001,438 +1877,438 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B9" s="11">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$E$2:$E$27)*B$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$E$2:$E$27)*B$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$E$2:$E$27)*B$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$E$2:$E$27)*B$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$E$2:$E$27)*B$7)</f>
-        <v>23</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*B$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*B$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*B$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*B$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*B$7)</f>
+        <v>17</v>
       </c>
       <c r="C9" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$E$2:$E$27)*C$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$E$2:$E$27)*C$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$E$2:$E$27)*C$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$E$2:$E$27)*C$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$E$2:$E$27)*C$7)</f>
-        <v>32.6</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*C$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*C$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*C$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*C$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*C$7)</f>
+        <v>32</v>
       </c>
       <c r="D9" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$E$2:$E$27)*D$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$E$2:$E$27)*D$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$E$2:$E$27)*D$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$E$2:$E$27)*D$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$E$2:$E$27)*D$7)</f>
-        <v>26.400000000000002</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*D$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*D$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*D$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*D$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*D$7)</f>
+        <v>25.8</v>
       </c>
       <c r="E9" s="12">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$E$2:$E$27)*E$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$E$2:$E$27)*E$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$E$2:$E$27)*E$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$E$2:$E$27)*E$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$E$2:$E$27)*E$7)</f>
-        <v>23</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*E$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*E$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*E$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*E$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*E$7)</f>
+        <v>17</v>
       </c>
       <c r="F9" s="11">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$E$2:$E$27)*F$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$E$2:$E$27)*F$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$E$2:$E$27)*F$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$E$2:$E$27)*F$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$E$2:$E$27)*F$7)</f>
-        <v>23</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*F$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*F$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*F$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*F$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*F$7)</f>
+        <v>17</v>
       </c>
       <c r="G9" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$E$2:$E$27)*G$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$E$2:$E$27)*G$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$E$2:$E$27)*G$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$E$2:$E$27)*G$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$E$2:$E$27)*G$7)</f>
-        <v>44.6</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*G$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*G$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*G$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*G$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*G$7)</f>
+        <v>14.09</v>
       </c>
       <c r="H9" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$E$2:$E$27)*H$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$E$2:$E$27)*H$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$E$2:$E$27)*H$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$E$2:$E$27)*H$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$E$2:$E$27)*H$7)</f>
-        <v>29</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*H$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*H$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*H$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*H$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*H$7)</f>
+        <v>18.115000000000002</v>
       </c>
       <c r="I9" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$E$2:$E$27)*I$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$E$2:$E$27)*I$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$E$2:$E$27)*I$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$E$2:$E$27)*I$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$E$2:$E$27)*I$7)</f>
-        <v>44.6</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*I$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*I$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*I$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*I$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*I$7)</f>
+        <v>14.09</v>
       </c>
       <c r="J9" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$E$2:$E$27)*J$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$E$2:$E$27)*J$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$E$2:$E$27)*J$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$E$2:$E$27)*J$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$E$2:$E$27)*J$7)</f>
-        <v>29</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*J$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*J$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*J$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*J$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*J$7)</f>
+        <v>18.115000000000002</v>
       </c>
       <c r="K9" s="12">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$E$2:$E$27)*K$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$E$2:$E$27)*K$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$E$2:$E$27)*K$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$E$2:$E$27)*K$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$E$2:$E$27)*K$7)</f>
-        <v>44.6</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*K$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*K$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*K$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*K$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*K$7)</f>
+        <v>14.09</v>
       </c>
       <c r="L9" s="11">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$E$2:$E$27)*L$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$E$2:$E$27)*L$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$E$2:$E$27)*L$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$E$2:$E$27)*L$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$E$2:$E$27)*L$7)</f>
-        <v>29</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*L$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*L$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*L$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*L$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*L$7)</f>
+        <v>18.115000000000002</v>
       </c>
       <c r="M9" s="12">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$E$2:$E$27)*M$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$E$2:$E$27)*M$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$E$2:$E$27)*M$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$E$2:$E$27)*M$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$E$2:$E$27)*M$7)</f>
-        <v>44.6</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*M$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*M$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*M$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*M$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*M$7)</f>
+        <v>14.09</v>
       </c>
       <c r="N9" s="19">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$E$2:$E$27)*N$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$E$2:$E$27)*N$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$E$2:$E$27)*N$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$E$2:$E$27)*N$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$E$2:$E$27)*N$7)</f>
-        <v>23</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*N$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*N$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*N$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*N$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*N$7)</f>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B10" s="11">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$F$2:$F$27)*B$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$F$2:$F$27)*B$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$F$2:$F$27)*B$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$F$2:$F$27)*B$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$F$2:$F$27)*B$7)</f>
-        <v>502.3</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*B$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*B$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*B$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*B$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*B$7)</f>
+        <v>358.3</v>
       </c>
       <c r="C10" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$F$2:$F$27)*C$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$F$2:$F$27)*C$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$F$2:$F$27)*C$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$F$2:$F$27)*C$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$F$2:$F$27)*C$7)</f>
-        <v>695.55</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*C$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*C$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*C$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*C$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*C$7)</f>
+        <v>681.14999999999986</v>
       </c>
       <c r="D10" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$F$2:$F$27)*D$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$F$2:$F$27)*D$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$F$2:$F$27)*D$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$F$2:$F$27)*D$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$F$2:$F$27)*D$7)</f>
-        <v>509.59999999999991</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*D$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*D$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*D$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*D$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*D$7)</f>
+        <v>495.19999999999993</v>
       </c>
       <c r="E10" s="12">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$F$2:$F$27)*E$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$F$2:$F$27)*E$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$F$2:$F$27)*E$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$F$2:$F$27)*E$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$F$2:$F$27)*E$7)</f>
-        <v>502.3</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*E$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*E$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*E$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*E$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*E$7)</f>
+        <v>358.3</v>
       </c>
       <c r="F10" s="11">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$F$2:$F$27)*F$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$F$2:$F$27)*F$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$F$2:$F$27)*F$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$F$2:$F$27)*F$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$F$2:$F$27)*F$7)</f>
-        <v>502.3</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*F$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*F$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*F$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*F$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*F$7)</f>
+        <v>358.3</v>
       </c>
       <c r="G10" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$F$2:$F$27)*G$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$F$2:$F$27)*G$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$F$2:$F$27)*G$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$F$2:$F$27)*G$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$F$2:$F$27)*G$7)</f>
-        <v>1020.7</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*G$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*G$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*G$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*G$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*G$7)</f>
+        <v>288.46000000000004</v>
       </c>
       <c r="H10" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$F$2:$F$27)*H$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$F$2:$F$27)*H$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$F$2:$F$27)*H$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$F$2:$F$27)*H$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$F$2:$F$27)*H$7)</f>
-        <v>646.29999999999995</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*H$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*H$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*H$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*H$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*H$7)</f>
+        <v>385.06</v>
       </c>
       <c r="I10" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$F$2:$F$27)*I$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$F$2:$F$27)*I$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$F$2:$F$27)*I$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$F$2:$F$27)*I$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$F$2:$F$27)*I$7)</f>
-        <v>1020.7</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*I$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*I$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*I$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*I$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*I$7)</f>
+        <v>288.46000000000004</v>
       </c>
       <c r="J10" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$F$2:$F$27)*J$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$F$2:$F$27)*J$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$F$2:$F$27)*J$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$F$2:$F$27)*J$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$F$2:$F$27)*J$7)</f>
-        <v>646.29999999999995</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*J$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*J$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*J$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*J$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*J$7)</f>
+        <v>385.06</v>
       </c>
       <c r="K10" s="12">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$F$2:$F$27)*K$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$F$2:$F$27)*K$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$F$2:$F$27)*K$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$F$2:$F$27)*K$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$F$2:$F$27)*K$7)</f>
-        <v>1020.7</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*K$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*K$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*K$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*K$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*K$7)</f>
+        <v>288.46000000000004</v>
       </c>
       <c r="L10" s="11">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$F$2:$F$27)*L$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$F$2:$F$27)*L$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$F$2:$F$27)*L$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$F$2:$F$27)*L$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$F$2:$F$27)*L$7)</f>
-        <v>646.29999999999995</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*L$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*L$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*L$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*L$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*L$7)</f>
+        <v>385.06</v>
       </c>
       <c r="M10" s="12">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$F$2:$F$27)*M$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$F$2:$F$27)*M$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$F$2:$F$27)*M$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$F$2:$F$27)*M$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$F$2:$F$27)*M$7)</f>
-        <v>1020.7</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*M$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*M$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*M$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*M$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*M$7)</f>
+        <v>288.46000000000004</v>
       </c>
       <c r="N10" s="19">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$F$2:$F$27)*N$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$F$2:$F$27)*N$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$F$2:$F$27)*N$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$F$2:$F$27)*N$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$F$2:$F$27)*N$7)</f>
-        <v>502.3</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*N$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*N$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*N$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*N$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*N$7)</f>
+        <v>358.3</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B11" s="11">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$G$2:$G$27)*B$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$G$2:$G$27)*B$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$G$2:$G$27)*B$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$G$2:$G$27)*B$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$G$2:$G$27)*B$7)</f>
-        <v>192</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*B$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*B$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*B$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*B$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*B$7)</f>
+        <v>132</v>
       </c>
       <c r="C11" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$G$2:$G$27)*C$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$G$2:$G$27)*C$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$G$2:$G$27)*C$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$G$2:$G$27)*C$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$G$2:$G$27)*C$7)</f>
-        <v>79.5</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*C$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*C$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*C$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*C$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*C$7)</f>
+        <v>73.5</v>
       </c>
       <c r="D11" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$G$2:$G$27)*D$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$G$2:$G$27)*D$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$G$2:$G$27)*D$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$G$2:$G$27)*D$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$G$2:$G$27)*D$7)</f>
-        <v>69</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*D$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*D$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*D$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*D$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*D$7)</f>
+        <v>63</v>
       </c>
       <c r="E11" s="12">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$G$2:$G$27)*E$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$G$2:$G$27)*E$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$G$2:$G$27)*E$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$G$2:$G$27)*E$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$G$2:$G$27)*E$7)</f>
-        <v>192</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*E$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*E$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*E$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*E$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*E$7)</f>
+        <v>132</v>
       </c>
       <c r="F11" s="11">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$G$2:$G$27)*F$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$G$2:$G$27)*F$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$G$2:$G$27)*F$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$G$2:$G$27)*F$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$G$2:$G$27)*F$7)</f>
-        <v>192</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*F$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*F$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*F$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*F$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*F$7)</f>
+        <v>132</v>
       </c>
       <c r="G11" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$G$2:$G$27)*G$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$G$2:$G$27)*G$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$G$2:$G$27)*G$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$G$2:$G$27)*G$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$G$2:$G$27)*G$7)</f>
-        <v>111</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*G$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*G$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*G$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*G$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*G$7)</f>
+        <v>78</v>
       </c>
       <c r="H11" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$G$2:$G$27)*H$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$G$2:$G$27)*H$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$G$2:$G$27)*H$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$G$2:$G$27)*H$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$G$2:$G$27)*H$7)</f>
-        <v>202.5</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*H$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*H$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*H$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*H$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*H$7)</f>
+        <v>139</v>
       </c>
       <c r="I11" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$G$2:$G$27)*I$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$G$2:$G$27)*I$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$G$2:$G$27)*I$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$G$2:$G$27)*I$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$G$2:$G$27)*I$7)</f>
-        <v>111</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*I$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*I$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*I$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*I$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*I$7)</f>
+        <v>78</v>
       </c>
       <c r="J11" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$G$2:$G$27)*J$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$G$2:$G$27)*J$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$G$2:$G$27)*J$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$G$2:$G$27)*J$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$G$2:$G$27)*J$7)</f>
-        <v>202.5</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*J$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*J$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*J$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*J$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*J$7)</f>
+        <v>139</v>
       </c>
       <c r="K11" s="12">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$G$2:$G$27)*K$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$G$2:$G$27)*K$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$G$2:$G$27)*K$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$G$2:$G$27)*K$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$G$2:$G$27)*K$7)</f>
-        <v>111</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*K$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*K$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*K$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*K$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*K$7)</f>
+        <v>78</v>
       </c>
       <c r="L11" s="11">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$G$2:$G$27)*L$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$G$2:$G$27)*L$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$G$2:$G$27)*L$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$G$2:$G$27)*L$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$G$2:$G$27)*L$7)</f>
-        <v>202.5</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*L$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*L$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*L$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*L$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*L$7)</f>
+        <v>139</v>
       </c>
       <c r="M11" s="12">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$G$2:$G$27)*M$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$G$2:$G$27)*M$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$G$2:$G$27)*M$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$G$2:$G$27)*M$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$G$2:$G$27)*M$7)</f>
-        <v>111</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*M$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*M$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*M$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*M$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*M$7)</f>
+        <v>78</v>
       </c>
       <c r="N11" s="19">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$G$2:$G$27)*N$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$G$2:$G$27)*N$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$G$2:$G$27)*N$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$G$2:$G$27)*N$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$G$2:$G$27)*N$7)</f>
-        <v>192</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*N$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*N$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*N$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*N$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*N$7)</f>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B12" s="11">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$H$2:$H$27)*B$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$H$2:$H$27)*B$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$H$2:$H$27)*B$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$H$2:$H$27)*B$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$H$2:$H$27)*B$7)</f>
-        <v>4456.6000000000004</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*B$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*B$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*B$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*B$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*B$7)</f>
+        <v>3016.6</v>
       </c>
       <c r="C12" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$H$2:$H$27)*C$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$H$2:$H$27)*C$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$H$2:$H$27)*C$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$H$2:$H$27)*C$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$H$2:$H$27)*C$7)</f>
-        <v>1684.35</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*C$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*C$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*C$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*C$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*C$7)</f>
+        <v>1540.35</v>
       </c>
       <c r="D12" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$H$2:$H$27)*D$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$H$2:$H$27)*D$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$H$2:$H$27)*D$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$H$2:$H$27)*D$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$H$2:$H$27)*D$7)</f>
-        <v>1360.1</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*D$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*D$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*D$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*D$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*D$7)</f>
+        <v>1216.0999999999999</v>
       </c>
       <c r="E12" s="12">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$H$2:$H$27)*E$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$H$2:$H$27)*E$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$H$2:$H$27)*E$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$H$2:$H$27)*E$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$H$2:$H$27)*E$7)</f>
-        <v>4456.6000000000004</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*E$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*E$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*E$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*E$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*E$7)</f>
+        <v>3016.6</v>
       </c>
       <c r="F12" s="11">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$H$2:$H$27)*F$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$H$2:$H$27)*F$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$H$2:$H$27)*F$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$H$2:$H$27)*F$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$H$2:$H$27)*F$7)</f>
-        <v>4456.6000000000004</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*F$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*F$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*F$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*F$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*F$7)</f>
+        <v>3016.6</v>
       </c>
       <c r="G12" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$H$2:$H$27)*G$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$H$2:$H$27)*G$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$H$2:$H$27)*G$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$H$2:$H$27)*G$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$H$2:$H$27)*G$7)</f>
-        <v>2512.6</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*G$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*G$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*G$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*G$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*G$7)</f>
+        <v>1720.6</v>
       </c>
       <c r="H12" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$H$2:$H$27)*H$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$H$2:$H$27)*H$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$H$2:$H$27)*H$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$H$2:$H$27)*H$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$H$2:$H$27)*H$7)</f>
-        <v>4708.6000000000004</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*H$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*H$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*H$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*H$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*H$7)</f>
+        <v>3184.6</v>
       </c>
       <c r="I12" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$H$2:$H$27)*I$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$H$2:$H$27)*I$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$H$2:$H$27)*I$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$H$2:$H$27)*I$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$H$2:$H$27)*I$7)</f>
-        <v>2512.6</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*I$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*I$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*I$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*I$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*I$7)</f>
+        <v>1720.6</v>
       </c>
       <c r="J12" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$H$2:$H$27)*J$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$H$2:$H$27)*J$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$H$2:$H$27)*J$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$H$2:$H$27)*J$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$H$2:$H$27)*J$7)</f>
-        <v>4708.6000000000004</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*J$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*J$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*J$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*J$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*J$7)</f>
+        <v>3184.6</v>
       </c>
       <c r="K12" s="12">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$H$2:$H$27)*K$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$H$2:$H$27)*K$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$H$2:$H$27)*K$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$H$2:$H$27)*K$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$H$2:$H$27)*K$7)</f>
-        <v>2512.6</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*K$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*K$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*K$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*K$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*K$7)</f>
+        <v>1720.6</v>
       </c>
       <c r="L12" s="11">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$H$2:$H$27)*L$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$H$2:$H$27)*L$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$H$2:$H$27)*L$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$H$2:$H$27)*L$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$H$2:$H$27)*L$7)</f>
-        <v>4708.6000000000004</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*L$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*L$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*L$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*L$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*L$7)</f>
+        <v>3184.6</v>
       </c>
       <c r="M12" s="12">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$H$2:$H$27)*M$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$H$2:$H$27)*M$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$H$2:$H$27)*M$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$H$2:$H$27)*M$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$H$2:$H$27)*M$7)</f>
-        <v>2512.6</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*M$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*M$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*M$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*M$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*M$7)</f>
+        <v>1720.6</v>
       </c>
       <c r="N12" s="19">
-        <f>(SUMIF(Component_Specs!$C$2:$C$27,$A$3,Component_Specs!$H$2:$H$27)*N$3)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$4,Component_Specs!$H$2:$H$27)*N$4)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$5,Component_Specs!$H$2:$H$27)*N$5)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$6,Component_Specs!$H$2:$H$27)*N$6)
-+(SUMIF(Component_Specs!$C$2:$C$27,$A$7,Component_Specs!$H$2:$H$27)*N$7)</f>
-        <v>4456.6000000000004</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*N$3)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*N$4)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*N$5)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*N$6)
++(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*N$7)</f>
+        <v>3016.6</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
@@ -2447,132 +2323,132 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B14" s="23">
         <f>B9*Mission_Phases!$B3/60</f>
-        <v>1.9166666666666667</v>
+        <v>1.4166666666666667</v>
       </c>
       <c r="C14" s="24">
         <f>C9*Mission_Phases!$B4/60</f>
-        <v>5.4333333333333336</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="D14" s="24">
         <f>D9*Mission_Phases!$B5/60</f>
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="E14" s="25">
         <f>E9*Mission_Phases!$B6/60</f>
-        <v>1.9166666666666667</v>
+        <v>1.4166666666666667</v>
       </c>
       <c r="F14" s="23">
         <f>F9*Mission_Phases!$B9/60</f>
-        <v>3.8333333333333335</v>
+        <v>2.8333333333333335</v>
       </c>
       <c r="G14" s="24">
         <f>G9*Mission_Phases!$B10/60</f>
-        <v>7.4333333333333336</v>
+        <v>2.3483333333333336</v>
       </c>
       <c r="H14" s="24">
         <f>H9*Mission_Phases!$B11/60</f>
-        <v>4.833333333333333</v>
+        <v>3.0191666666666674</v>
       </c>
       <c r="I14" s="24">
         <f>I9*Mission_Phases!$B12/60</f>
-        <v>7.4333333333333336</v>
+        <v>2.3483333333333336</v>
       </c>
       <c r="J14" s="24">
         <f>J9*Mission_Phases!$B13/60</f>
-        <v>4.833333333333333</v>
+        <v>3.0191666666666674</v>
       </c>
       <c r="K14" s="25">
         <f>K9*Mission_Phases!$B14/60</f>
-        <v>7.4333333333333336</v>
+        <v>2.3483333333333336</v>
       </c>
       <c r="L14" s="23">
         <f>L9*Mission_Phases!$B17/60</f>
-        <v>2.4166666666666665</v>
+        <v>1.5095833333333337</v>
       </c>
       <c r="M14" s="25">
         <f>M9*Mission_Phases!$B18/60</f>
-        <v>18.583333333333332</v>
+        <v>5.8708333333333336</v>
       </c>
       <c r="N14" s="26">
         <f>N9*Mission_Phases!$B21/60</f>
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B15" s="11">
         <f>B10*Mission_Phases!B3/60</f>
-        <v>41.858333333333334</v>
+        <v>29.858333333333334</v>
       </c>
       <c r="C15" s="1">
         <f>C10*Mission_Phases!B4/60</f>
-        <v>115.925</v>
+        <v>113.52499999999996</v>
       </c>
       <c r="D15" s="1">
         <f>D10*Mission_Phases!B5/60</f>
-        <v>84.933333333333323</v>
+        <v>82.533333333333317</v>
       </c>
       <c r="E15" s="12">
         <f>E10*Mission_Phases!B6/60</f>
-        <v>41.858333333333334</v>
+        <v>29.858333333333334</v>
       </c>
       <c r="F15" s="11">
         <f>F10*Mission_Phases!B9/60</f>
-        <v>83.716666666666669</v>
+        <v>59.716666666666669</v>
       </c>
       <c r="G15" s="1">
         <f>G10*Mission_Phases!$B10/60</f>
-        <v>170.11666666666667</v>
+        <v>48.076666666666675</v>
       </c>
       <c r="H15" s="1">
         <f>H10*Mission_Phases!$B11/60</f>
-        <v>107.71666666666667</v>
+        <v>64.176666666666662</v>
       </c>
       <c r="I15" s="1">
         <f>I10*Mission_Phases!$B12/60</f>
-        <v>170.11666666666667</v>
+        <v>48.076666666666675</v>
       </c>
       <c r="J15" s="1">
         <f>J10*Mission_Phases!$B13/60</f>
-        <v>107.71666666666667</v>
+        <v>64.176666666666662</v>
       </c>
       <c r="K15" s="12">
         <f>K10*Mission_Phases!$B14/60</f>
-        <v>170.11666666666667</v>
+        <v>48.076666666666675</v>
       </c>
       <c r="L15" s="11">
         <f>L10*Mission_Phases!$B17/60</f>
-        <v>53.858333333333334</v>
+        <v>32.088333333333331</v>
       </c>
       <c r="M15" s="12">
         <f>M10*Mission_Phases!$B18/60</f>
-        <v>425.29166666666669</v>
+        <v>120.19166666666668</v>
       </c>
       <c r="N15" s="19">
         <f>N10*Mission_Phases!$B21/60</f>
-        <v>251.15</v>
+        <v>179.15</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B16" s="11">
         <f>SUM(B15:E15)</f>
-        <v>284.57499999999999</v>
+        <v>255.77499999999998</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="12"/>
       <c r="F16" s="11">
         <f>SUM(F15:K15)</f>
-        <v>809.50000000000011</v>
+        <v>332.3</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -2581,28 +2457,28 @@
       <c r="K16" s="12"/>
       <c r="L16" s="11">
         <f>SUM(L15:M15)</f>
-        <v>479.15000000000003</v>
+        <v>152.28</v>
       </c>
       <c r="M16" s="12"/>
       <c r="N16" s="19">
         <f>N15</f>
-        <v>251.15</v>
+        <v>179.15</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B17" s="13">
         <f>SUM(B14:E14)</f>
-        <v>13.666666666666666</v>
+        <v>12.466666666666667</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="20"/>
       <c r="E17" s="21"/>
       <c r="F17" s="13">
         <f>SUM(F14:K14)</f>
-        <v>35.799999999999997</v>
+        <v>15.916666666666668</v>
       </c>
       <c r="G17" s="20"/>
       <c r="H17" s="20"/>
@@ -2611,28 +2487,28 @@
       <c r="K17" s="21"/>
       <c r="L17" s="13">
         <f>SUM(L14:M14)</f>
-        <v>21</v>
+        <v>7.3804166666666671</v>
       </c>
       <c r="M17" s="21"/>
       <c r="N17" s="22">
         <f>N14</f>
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B18" s="13">
         <f>MAX(B9:E9)</f>
-        <v>32.6</v>
+        <v>32</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
       <c r="E18" s="15"/>
       <c r="F18" s="13">
         <f>MAX(F9:K9)</f>
-        <v>44.6</v>
+        <v>18.115000000000002</v>
       </c>
       <c r="G18" s="14"/>
       <c r="H18" s="14"/>
@@ -2641,12 +2517,12 @@
       <c r="K18" s="15"/>
       <c r="L18" s="13">
         <f>MAX(L9:M9)</f>
-        <v>44.6</v>
+        <v>18.115000000000002</v>
       </c>
       <c r="M18" s="15"/>
       <c r="N18" s="22">
         <f>N9</f>
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/calculations/System_Calculations.xlsx
+++ b/calculations/System_Calculations.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bobbystyles/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bobbystyles/Desktop/MRC/Git/24v-24v-converter/calculations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C206C0D9-2430-D54A-95F3-5DE1A1DA2EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A37A6F-8055-3E49-9761-17CCD19E56FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1820" yWindow="980" windowWidth="26420" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -794,22 +794,22 @@
         <v>3</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F23" si="0">A3*E3</f>
+        <f t="shared" ref="F3:F20" si="0">A3*E3</f>
         <v>72</v>
       </c>
       <c r="G3">
         <v>30</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H23" si="1">A3*G3</f>
+        <f t="shared" ref="H3:H20" si="1">A3*G3</f>
         <v>720</v>
       </c>
       <c r="K3" t="s">
         <v>28</v>
       </c>
       <c r="L3" s="1">
-        <f>SUMIF($D$2:$D$23,"Rover",$E$2:$E$23)
-+ SUMIF($D$2:$D$23,"Arm",$E$2:$E$23)</f>
+        <f>SUMIF($D$2:$D$14,"Rover",$E$2:$E$14)
++ SUMIF($D$2:$D$14,"Arm",$E$2:$E$14)</f>
         <v>39.299999999999997</v>
       </c>
     </row>
@@ -844,8 +844,8 @@
         <v>29</v>
       </c>
       <c r="L4" s="1">
-        <f>SUMIF($D$2:$D$23,"Rover",$F$2:$F$23)
-+ SUMIF($D$2:$D$23,"Arm",$F$2:$F$23)</f>
+        <f>SUMIF($D$2:$D$20,"Rover",$F$2:$F$20)
++ SUMIF($D$2:$D$20,"Arm",$F$2:$F$20)</f>
         <v>893.5</v>
       </c>
     </row>
@@ -967,9 +967,9 @@
         <v>28</v>
       </c>
       <c r="L8" s="1">
-        <f>SUMIF($D$2:$D$23,"Rover",$E$2:$E$23)
-+ SUMIF($D$2:$D$23,"LD",$E$2:$E$23)</f>
-        <v>52.6</v>
+        <f>SUMIF($D$2:$D$20,"Rover",$E$2:$E$20)
++ SUMIF($D$2:$D$20,"LD",$E$2:$E$20)</f>
+        <v>20.6</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -1003,9 +1003,9 @@
         <v>29</v>
       </c>
       <c r="L9" s="1">
-        <f>SUMIF($D$2:$D$23,"Rover",$F$2:$F$23)
-+ SUMIF($D$2:$D$23,"LD",$F$2:$F$23)</f>
-        <v>1138.3999999999999</v>
+        <f>SUMIF($D$2:$D$20,"Rover",$F$2:$F$20)
++ SUMIF($D$2:$D$20,"LD",$F$2:$F$20)</f>
+        <v>370.4</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
@@ -1013,91 +1013,91 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E10">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F10">
         <f t="shared" si="0"/>
-        <v>384</v>
+        <v>24</v>
       </c>
       <c r="G10">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="H10">
         <f t="shared" si="1"/>
-        <v>720</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F11">
         <f t="shared" si="0"/>
-        <v>192</v>
+        <v>38</v>
       </c>
       <c r="G11">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H11">
         <f t="shared" si="1"/>
-        <v>384</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F12">
         <f t="shared" si="0"/>
-        <v>192</v>
+        <v>5</v>
       </c>
       <c r="G12">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H12">
         <f t="shared" si="1"/>
-        <v>384</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>24</v>
+        <v>3.3</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
         <v>53</v>
@@ -1106,26 +1106,26 @@
         <v>18</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F13">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>1.65</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13">
         <f t="shared" si="1"/>
-        <v>48</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>19</v>
+        <v>3.3</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
         <v>53</v>
@@ -1134,46 +1134,46 @@
         <v>18</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="F14">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>1.65</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H14">
         <f t="shared" si="1"/>
-        <v>57</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F15">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>1.65</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H15">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
@@ -1181,13 +1181,13 @@
         <v>3.3</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E16">
         <v>0.5</v>
@@ -1209,13 +1209,13 @@
         <v>3.3</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E17">
         <v>0.5</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" t="s">
         <v>52</v>
@@ -1302,54 +1302,54 @@
         <v>20</v>
       </c>
       <c r="E20">
-        <v>0.5</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F20">
         <f t="shared" si="0"/>
-        <v>1.65</v>
+        <v>3.8500000000000005</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20">
         <f t="shared" si="1"/>
-        <v>3.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>3.3</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="D21" t="s">
         <v>20</v>
       </c>
       <c r="E21">
-        <v>0.5</v>
+        <v>16</v>
       </c>
       <c r="F21">
-        <f t="shared" si="0"/>
-        <v>1.65</v>
+        <f>A21*E21</f>
+        <v>384</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H21">
-        <f t="shared" si="1"/>
-        <v>3.3</v>
+        <f>A21*G21</f>
+        <v>720</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>3.3</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
         <v>52</v>
@@ -1358,26 +1358,26 @@
         <v>20</v>
       </c>
       <c r="E22">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="F22">
-        <f t="shared" si="0"/>
-        <v>1.65</v>
+        <f>A22*E22</f>
+        <v>192</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H22">
-        <f t="shared" si="1"/>
-        <v>3.3</v>
+        <f>A22*G22</f>
+        <v>384</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>3.5</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
         <v>52</v>
@@ -1386,18 +1386,18 @@
         <v>20</v>
       </c>
       <c r="E23">
-        <v>1.1000000000000001</v>
+        <v>8</v>
       </c>
       <c r="F23">
-        <f t="shared" si="0"/>
-        <v>3.8500000000000005</v>
+        <f>A23*E23</f>
+        <v>192</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H23">
-        <f t="shared" si="1"/>
-        <v>7</v>
+        <f>A23*G23</f>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -1880,107 +1880,107 @@
         <v>55</v>
       </c>
       <c r="B9" s="11">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*B$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*B$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*B$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*B$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*B$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$E$2:$E$20)*B$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$E$2:$E$20)*B$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$E$2:$E$20)*B$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$E$2:$E$20)*B$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$E$2:$E$20)*B$7)</f>
         <v>17</v>
       </c>
       <c r="C9" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*C$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*C$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*C$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*C$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*C$7)</f>
-        <v>32</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$E$2:$E$20)*C$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$E$2:$E$20)*C$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$E$2:$E$20)*C$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$E$2:$E$20)*C$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$E$2:$E$20)*C$7)</f>
+        <v>8</v>
       </c>
       <c r="D9" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*D$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*D$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*D$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*D$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*D$7)</f>
-        <v>25.8</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$E$2:$E$20)*D$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$E$2:$E$20)*D$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$E$2:$E$20)*D$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$E$2:$E$20)*D$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$E$2:$E$20)*D$7)</f>
+        <v>9.8000000000000007</v>
       </c>
       <c r="E9" s="12">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*E$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*E$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*E$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*E$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*E$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$E$2:$E$20)*E$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$E$2:$E$20)*E$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$E$2:$E$20)*E$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$E$2:$E$20)*E$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$E$2:$E$20)*E$7)</f>
         <v>17</v>
       </c>
       <c r="F9" s="11">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*F$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*F$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*F$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*F$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*F$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$E$2:$E$20)*F$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$E$2:$E$20)*F$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$E$2:$E$20)*F$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$E$2:$E$20)*F$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$E$2:$E$20)*F$7)</f>
         <v>17</v>
       </c>
       <c r="G9" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*G$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*G$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*G$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*G$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*G$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$E$2:$E$20)*G$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$E$2:$E$20)*G$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$E$2:$E$20)*G$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$E$2:$E$20)*G$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$E$2:$E$20)*G$7)</f>
         <v>14.09</v>
       </c>
       <c r="H9" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*H$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*H$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*H$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*H$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*H$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$E$2:$E$20)*H$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$E$2:$E$20)*H$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$E$2:$E$20)*H$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$E$2:$E$20)*H$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$E$2:$E$20)*H$7)</f>
         <v>18.115000000000002</v>
       </c>
       <c r="I9" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*I$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*I$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*I$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*I$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*I$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$E$2:$E$20)*I$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$E$2:$E$20)*I$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$E$2:$E$20)*I$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$E$2:$E$20)*I$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$E$2:$E$20)*I$7)</f>
         <v>14.09</v>
       </c>
       <c r="J9" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*J$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*J$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*J$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*J$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*J$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$E$2:$E$20)*J$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$E$2:$E$20)*J$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$E$2:$E$20)*J$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$E$2:$E$20)*J$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$E$2:$E$20)*J$7)</f>
         <v>18.115000000000002</v>
       </c>
       <c r="K9" s="12">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*K$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*K$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*K$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*K$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*K$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$E$2:$E$20)*K$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$E$2:$E$20)*K$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$E$2:$E$20)*K$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$E$2:$E$20)*K$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$E$2:$E$20)*K$7)</f>
         <v>14.09</v>
       </c>
       <c r="L9" s="11">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*L$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*L$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*L$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*L$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*L$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$E$2:$E$20)*L$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$E$2:$E$20)*L$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$E$2:$E$20)*L$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$E$2:$E$20)*L$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$E$2:$E$20)*L$7)</f>
         <v>18.115000000000002</v>
       </c>
       <c r="M9" s="12">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*M$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*M$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*M$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*M$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*M$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$E$2:$E$20)*M$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$E$2:$E$20)*M$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$E$2:$E$20)*M$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$E$2:$E$20)*M$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$E$2:$E$20)*M$7)</f>
         <v>14.09</v>
       </c>
       <c r="N9" s="19">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$E$2:$E$23)*N$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$E$2:$E$23)*N$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$E$2:$E$23)*N$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$E$2:$E$23)*N$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$E$2:$E$23)*N$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$E$2:$E$20)*N$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$E$2:$E$20)*N$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$E$2:$E$20)*N$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$E$2:$E$20)*N$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$E$2:$E$20)*N$7)</f>
         <v>17</v>
       </c>
     </row>
@@ -1989,107 +1989,107 @@
         <v>56</v>
       </c>
       <c r="B10" s="11">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*B$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*B$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*B$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*B$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*B$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$F$2:$F$20)*B$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$F$2:$F$20)*B$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$F$2:$F$20)*B$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$F$2:$F$20)*B$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$F$2:$F$20)*B$7)</f>
         <v>358.3</v>
       </c>
       <c r="C10" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*C$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*C$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*C$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*C$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*C$7)</f>
-        <v>681.14999999999986</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$F$2:$F$20)*C$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$F$2:$F$20)*C$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$F$2:$F$20)*C$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$F$2:$F$20)*C$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$F$2:$F$20)*C$7)</f>
+        <v>105.15</v>
       </c>
       <c r="D10" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*D$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*D$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*D$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*D$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*D$7)</f>
-        <v>495.19999999999993</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$F$2:$F$20)*D$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$F$2:$F$20)*D$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$F$2:$F$20)*D$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$F$2:$F$20)*D$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$F$2:$F$20)*D$7)</f>
+        <v>111.20000000000002</v>
       </c>
       <c r="E10" s="12">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*E$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*E$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*E$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*E$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*E$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$F$2:$F$20)*E$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$F$2:$F$20)*E$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$F$2:$F$20)*E$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$F$2:$F$20)*E$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$F$2:$F$20)*E$7)</f>
         <v>358.3</v>
       </c>
       <c r="F10" s="11">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*F$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*F$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*F$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*F$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*F$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$F$2:$F$20)*F$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$F$2:$F$20)*F$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$F$2:$F$20)*F$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$F$2:$F$20)*F$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$F$2:$F$20)*F$7)</f>
         <v>358.3</v>
       </c>
       <c r="G10" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*G$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*G$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*G$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*G$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*G$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$F$2:$F$20)*G$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$F$2:$F$20)*G$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$F$2:$F$20)*G$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$F$2:$F$20)*G$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$F$2:$F$20)*G$7)</f>
         <v>288.46000000000004</v>
       </c>
       <c r="H10" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*H$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*H$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*H$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*H$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*H$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$F$2:$F$20)*H$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$F$2:$F$20)*H$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$F$2:$F$20)*H$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$F$2:$F$20)*H$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$F$2:$F$20)*H$7)</f>
         <v>385.06</v>
       </c>
       <c r="I10" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*I$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*I$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*I$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*I$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*I$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$F$2:$F$20)*I$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$F$2:$F$20)*I$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$F$2:$F$20)*I$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$F$2:$F$20)*I$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$F$2:$F$20)*I$7)</f>
         <v>288.46000000000004</v>
       </c>
       <c r="J10" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*J$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*J$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*J$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*J$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*J$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$F$2:$F$20)*J$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$F$2:$F$20)*J$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$F$2:$F$20)*J$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$F$2:$F$20)*J$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$F$2:$F$20)*J$7)</f>
         <v>385.06</v>
       </c>
       <c r="K10" s="12">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*K$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*K$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*K$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*K$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*K$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$F$2:$F$20)*K$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$F$2:$F$20)*K$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$F$2:$F$20)*K$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$F$2:$F$20)*K$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$F$2:$F$20)*K$7)</f>
         <v>288.46000000000004</v>
       </c>
       <c r="L10" s="11">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*L$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*L$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*L$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*L$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*L$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$F$2:$F$20)*L$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$F$2:$F$20)*L$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$F$2:$F$20)*L$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$F$2:$F$20)*L$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$F$2:$F$20)*L$7)</f>
         <v>385.06</v>
       </c>
       <c r="M10" s="12">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*M$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*M$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*M$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*M$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*M$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$F$2:$F$20)*M$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$F$2:$F$20)*M$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$F$2:$F$20)*M$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$F$2:$F$20)*M$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$F$2:$F$20)*M$7)</f>
         <v>288.46000000000004</v>
       </c>
       <c r="N10" s="19">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$F$2:$F$23)*N$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$F$2:$F$23)*N$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$F$2:$F$23)*N$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$F$2:$F$23)*N$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$F$2:$F$23)*N$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$F$2:$F$20)*N$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$F$2:$F$20)*N$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$F$2:$F$20)*N$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$F$2:$F$20)*N$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$F$2:$F$20)*N$7)</f>
         <v>358.3</v>
       </c>
     </row>
@@ -2098,107 +2098,107 @@
         <v>57</v>
       </c>
       <c r="B11" s="11">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*B$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*B$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*B$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*B$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*B$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$G$2:$G$20)*B$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$G$2:$G$20)*B$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$G$2:$G$20)*B$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$G$2:$G$20)*B$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$G$2:$G$20)*B$7)</f>
         <v>132</v>
       </c>
       <c r="C11" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*C$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*C$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*C$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*C$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*C$7)</f>
-        <v>73.5</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$G$2:$G$20)*C$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$G$2:$G$20)*C$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$G$2:$G$20)*C$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$G$2:$G$20)*C$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$G$2:$G$20)*C$7)</f>
+        <v>27.5</v>
       </c>
       <c r="D11" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*D$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*D$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*D$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*D$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*D$7)</f>
-        <v>63</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$G$2:$G$20)*D$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$G$2:$G$20)*D$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$G$2:$G$20)*D$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$G$2:$G$20)*D$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$G$2:$G$20)*D$7)</f>
+        <v>31</v>
       </c>
       <c r="E11" s="12">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*E$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*E$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*E$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*E$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*E$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$G$2:$G$20)*E$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$G$2:$G$20)*E$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$G$2:$G$20)*E$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$G$2:$G$20)*E$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$G$2:$G$20)*E$7)</f>
         <v>132</v>
       </c>
       <c r="F11" s="11">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*F$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*F$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*F$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*F$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*F$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$G$2:$G$20)*F$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$G$2:$G$20)*F$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$G$2:$G$20)*F$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$G$2:$G$20)*F$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$G$2:$G$20)*F$7)</f>
         <v>132</v>
       </c>
       <c r="G11" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*G$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*G$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*G$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*G$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*G$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$G$2:$G$20)*G$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$G$2:$G$20)*G$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$G$2:$G$20)*G$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$G$2:$G$20)*G$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$G$2:$G$20)*G$7)</f>
         <v>78</v>
       </c>
       <c r="H11" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*H$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*H$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*H$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*H$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*H$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$G$2:$G$20)*H$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$G$2:$G$20)*H$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$G$2:$G$20)*H$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$G$2:$G$20)*H$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$G$2:$G$20)*H$7)</f>
         <v>139</v>
       </c>
       <c r="I11" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*I$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*I$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*I$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*I$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*I$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$G$2:$G$20)*I$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$G$2:$G$20)*I$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$G$2:$G$20)*I$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$G$2:$G$20)*I$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$G$2:$G$20)*I$7)</f>
         <v>78</v>
       </c>
       <c r="J11" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*J$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*J$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*J$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*J$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*J$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$G$2:$G$20)*J$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$G$2:$G$20)*J$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$G$2:$G$20)*J$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$G$2:$G$20)*J$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$G$2:$G$20)*J$7)</f>
         <v>139</v>
       </c>
       <c r="K11" s="12">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*K$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*K$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*K$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*K$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*K$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$G$2:$G$20)*K$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$G$2:$G$20)*K$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$G$2:$G$20)*K$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$G$2:$G$20)*K$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$G$2:$G$20)*K$7)</f>
         <v>78</v>
       </c>
       <c r="L11" s="11">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*L$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*L$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*L$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*L$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*L$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$G$2:$G$20)*L$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$G$2:$G$20)*L$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$G$2:$G$20)*L$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$G$2:$G$20)*L$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$G$2:$G$20)*L$7)</f>
         <v>139</v>
       </c>
       <c r="M11" s="12">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*M$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*M$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*M$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*M$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*M$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$G$2:$G$20)*M$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$G$2:$G$20)*M$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$G$2:$G$20)*M$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$G$2:$G$20)*M$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$G$2:$G$20)*M$7)</f>
         <v>78</v>
       </c>
       <c r="N11" s="19">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$G$2:$G$23)*N$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$G$2:$G$23)*N$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$G$2:$G$23)*N$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$G$2:$G$23)*N$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$G$2:$G$23)*N$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$G$2:$G$20)*N$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$G$2:$G$20)*N$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$G$2:$G$20)*N$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$G$2:$G$20)*N$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$G$2:$G$20)*N$7)</f>
         <v>132</v>
       </c>
     </row>
@@ -2207,107 +2207,107 @@
         <v>58</v>
       </c>
       <c r="B12" s="11">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*B$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*B$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*B$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*B$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*B$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$H$2:$H$20)*B$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$H$2:$H$20)*B$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$H$2:$H$20)*B$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$H$2:$H$20)*B$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$H$2:$H$20)*B$7)</f>
         <v>3016.6</v>
       </c>
       <c r="C12" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*C$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*C$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*C$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*C$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*C$7)</f>
-        <v>1540.35</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$H$2:$H$20)*C$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$H$2:$H$20)*C$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$H$2:$H$20)*C$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$H$2:$H$20)*C$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$H$2:$H$20)*C$7)</f>
+        <v>436.35</v>
       </c>
       <c r="D12" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*D$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*D$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*D$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*D$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*D$7)</f>
-        <v>1216.0999999999999</v>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$H$2:$H$20)*D$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$H$2:$H$20)*D$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$H$2:$H$20)*D$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$H$2:$H$20)*D$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$H$2:$H$20)*D$7)</f>
+        <v>448.1</v>
       </c>
       <c r="E12" s="12">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*E$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*E$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*E$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*E$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*E$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$H$2:$H$20)*E$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$H$2:$H$20)*E$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$H$2:$H$20)*E$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$H$2:$H$20)*E$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$H$2:$H$20)*E$7)</f>
         <v>3016.6</v>
       </c>
       <c r="F12" s="11">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*F$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*F$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*F$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*F$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*F$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$H$2:$H$20)*F$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$H$2:$H$20)*F$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$H$2:$H$20)*F$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$H$2:$H$20)*F$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$H$2:$H$20)*F$7)</f>
         <v>3016.6</v>
       </c>
       <c r="G12" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*G$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*G$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*G$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*G$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*G$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$H$2:$H$20)*G$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$H$2:$H$20)*G$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$H$2:$H$20)*G$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$H$2:$H$20)*G$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$H$2:$H$20)*G$7)</f>
         <v>1720.6</v>
       </c>
       <c r="H12" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*H$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*H$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*H$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*H$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*H$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$H$2:$H$20)*H$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$H$2:$H$20)*H$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$H$2:$H$20)*H$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$H$2:$H$20)*H$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$H$2:$H$20)*H$7)</f>
         <v>3184.6</v>
       </c>
       <c r="I12" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*I$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*I$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*I$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*I$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*I$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$H$2:$H$20)*I$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$H$2:$H$20)*I$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$H$2:$H$20)*I$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$H$2:$H$20)*I$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$H$2:$H$20)*I$7)</f>
         <v>1720.6</v>
       </c>
       <c r="J12" s="1">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*J$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*J$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*J$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*J$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*J$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$H$2:$H$20)*J$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$H$2:$H$20)*J$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$H$2:$H$20)*J$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$H$2:$H$20)*J$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$H$2:$H$20)*J$7)</f>
         <v>3184.6</v>
       </c>
       <c r="K12" s="12">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*K$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*K$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*K$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*K$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*K$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$H$2:$H$20)*K$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$H$2:$H$20)*K$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$H$2:$H$20)*K$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$H$2:$H$20)*K$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$H$2:$H$20)*K$7)</f>
         <v>1720.6</v>
       </c>
       <c r="L12" s="11">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*L$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*L$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*L$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*L$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*L$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$H$2:$H$20)*L$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$H$2:$H$20)*L$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$H$2:$H$20)*L$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$H$2:$H$20)*L$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$H$2:$H$20)*L$7)</f>
         <v>3184.6</v>
       </c>
       <c r="M12" s="12">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*M$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*M$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*M$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*M$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*M$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$H$2:$H$20)*M$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$H$2:$H$20)*M$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$H$2:$H$20)*M$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$H$2:$H$20)*M$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$H$2:$H$20)*M$7)</f>
         <v>1720.6</v>
       </c>
       <c r="N12" s="19">
-        <f>(SUMIF(Component_Specs!$C$2:$C$23,$A$3,Component_Specs!$H$2:$H$23)*N$3)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$4,Component_Specs!$H$2:$H$23)*N$4)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$5,Component_Specs!$H$2:$H$23)*N$5)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$6,Component_Specs!$H$2:$H$23)*N$6)
-+(SUMIF(Component_Specs!$C$2:$C$23,$A$7,Component_Specs!$H$2:$H$23)*N$7)</f>
+        <f>(SUMIF(Component_Specs!$C$2:$C$20,$A$3,Component_Specs!$H$2:$H$20)*N$3)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$4,Component_Specs!$H$2:$H$20)*N$4)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$5,Component_Specs!$H$2:$H$20)*N$5)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$6,Component_Specs!$H$2:$H$20)*N$6)
++(SUMIF(Component_Specs!$C$2:$C$20,$A$7,Component_Specs!$H$2:$H$20)*N$7)</f>
         <v>3016.6</v>
       </c>
     </row>
@@ -2331,11 +2331,11 @@
       </c>
       <c r="C14" s="24">
         <f>C9*Mission_Phases!$B4/60</f>
-        <v>5.333333333333333</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="D14" s="24">
         <f>D9*Mission_Phases!$B5/60</f>
-        <v>4.3</v>
+        <v>1.6333333333333333</v>
       </c>
       <c r="E14" s="25">
         <f>E9*Mission_Phases!$B6/60</f>
@@ -2388,11 +2388,11 @@
       </c>
       <c r="C15" s="1">
         <f>C10*Mission_Phases!B4/60</f>
-        <v>113.52499999999996</v>
+        <v>17.524999999999999</v>
       </c>
       <c r="D15" s="1">
         <f>D10*Mission_Phases!B5/60</f>
-        <v>82.533333333333317</v>
+        <v>18.533333333333339</v>
       </c>
       <c r="E15" s="12">
         <f>E10*Mission_Phases!B6/60</f>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B16" s="11">
         <f>SUM(B15:E15)</f>
-        <v>255.77499999999998</v>
+        <v>95.775000000000006</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B17" s="13">
         <f>SUM(B14:E14)</f>
-        <v>12.466666666666667</v>
+        <v>5.8</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="20"/>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B18" s="13">
         <f>MAX(B9:E9)</f>
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
